--- a/data/all_datasets/REDD/REDD_House6_stats/2026-04-20.xlsx
+++ b/data/all_datasets/REDD/REDD_House6_stats/2026-04-20.xlsx
@@ -460,10 +460,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.1052631578947368</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03703703703703703</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -482,10 +482,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07407407407407407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -515,10 +515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1481481481481481</v>
+        <v>0.05263157894736842</v>
       </c>
     </row>
     <row r="8">
@@ -526,10 +526,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.07407407407407407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -537,10 +537,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03703703703703703</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -551,7 +551,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.05263157894736842</v>
       </c>
     </row>
     <row r="11">
@@ -562,7 +562,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.05263157894736842</v>
       </c>
     </row>
     <row r="12">
@@ -606,7 +606,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.05263157894736842</v>
       </c>
     </row>
     <row r="16">
@@ -628,7 +628,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>0.07407407407407407</v>
+        <v>0.1052631578947368</v>
       </c>
     </row>
     <row r="18">
@@ -661,7 +661,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.05263157894736842</v>
       </c>
     </row>
     <row r="21">
@@ -683,7 +683,7 @@
         <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1578947368421053</v>
       </c>
     </row>
     <row r="23">
@@ -705,7 +705,7 @@
         <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1481481481481481</v>
+        <v>0.2105263157894737</v>
       </c>
     </row>
     <row r="25">
@@ -716,7 +716,7 @@
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1578947368421053</v>
       </c>
     </row>
   </sheetData>
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.947255369471357</v>
+        <v>9.307283360630688</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4959852250628165</v>
+        <v>0.6492865995095483</v>
       </c>
     </row>
     <row r="3">
@@ -773,7 +773,7 @@
         <v>1.33344995247638</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1336845231136048</v>
+        <v>0.09302297477283307</v>
       </c>
     </row>
     <row r="4">
@@ -786,7 +786,7 @@
         <v>1.241311395923509</v>
       </c>
       <c r="C4" t="n">
-        <v>0.124447206804679</v>
+        <v>0.08659528500022062</v>
       </c>
     </row>
     <row r="5">
@@ -799,7 +799,7 @@
         <v>0.924000893388922</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09263536179955049</v>
+        <v>0.06445934595158001</v>
       </c>
     </row>
     <row r="6">
@@ -812,7 +812,7 @@
         <v>0.7727007519020074</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07746682305976799</v>
+        <v>0.05390447719289472</v>
       </c>
     </row>
     <row r="7">
@@ -825,7 +825,7 @@
         <v>0.7558839424705931</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07578086015958121</v>
+        <v>0.05273131757292338</v>
       </c>
     </row>
   </sheetData>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.947255369471357</v>
+        <v>9.307283360630688</v>
       </c>
     </row>
     <row r="3">
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -1049,7 +1049,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -1141,7 +1141,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -1187,7 +1187,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1279,7 +1279,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -1325,7 +1325,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -1371,7 +1371,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -1417,7 +1417,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -1532,7 +1532,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -1555,7 +1555,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -1601,7 +1601,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -1693,7 +1693,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -1716,7 +1716,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -1739,7 +1739,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -1785,7 +1785,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -1969,7 +1969,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -2015,7 +2015,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -2061,7 +2061,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -2107,7 +2107,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -2153,7 +2153,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -2199,7 +2199,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -2245,7 +2245,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -2337,7 +2337,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
@@ -2406,7 +2406,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -2429,7 +2429,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
@@ -2475,7 +2475,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -2498,7 +2498,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -2613,7 +2613,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -2659,7 +2659,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
@@ -2682,7 +2682,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -2705,7 +2705,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -2728,7 +2728,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -2751,7 +2751,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -2774,7 +2774,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -2797,7 +2797,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -2820,7 +2820,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -2843,7 +2843,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -2866,7 +2866,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -2912,7 +2912,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -2935,7 +2935,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -2958,7 +2958,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -2981,7 +2981,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -3004,7 +3004,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -3027,7 +3027,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -3050,7 +3050,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -3073,7 +3073,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -3096,7 +3096,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -3119,7 +3119,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -3142,7 +3142,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -3188,7 +3188,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -3234,7 +3234,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -3257,7 +3257,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -3280,7 +3280,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -3303,7 +3303,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -3326,7 +3326,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -3349,7 +3349,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -3395,7 +3395,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>1020.245726495726</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -3418,7 +3418,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>1020.245726495726</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>1020.245726495726</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -3464,7 +3464,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>1020.245726495726</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -3487,7 +3487,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>1020.245726495726</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -3510,7 +3510,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>1020.245726495726</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -3533,7 +3533,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>1020.245726495726</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -3556,7 +3556,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>1020.245726495726</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -3579,7 +3579,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>1020.245726495726</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -3602,7 +3602,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>1020.245726495726</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>1020.245726495726</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>1020.245726495726</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -3671,7 +3671,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>1020.245726495726</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>1020.245726495726</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>1020.245726495726</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -3740,7 +3740,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -3763,7 +3763,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -3809,7 +3809,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -3832,7 +3832,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -3855,7 +3855,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -3901,7 +3901,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -3924,7 +3924,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -3947,7 +3947,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -3970,7 +3970,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -4016,7 +4016,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -4039,7 +4039,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -4085,7 +4085,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -4108,7 +4108,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -4154,7 +4154,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -4177,7 +4177,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -4200,7 +4200,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -4223,7 +4223,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -4246,7 +4246,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -4269,7 +4269,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -4292,7 +4292,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -4361,7 +4361,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -4407,7 +4407,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -4430,7 +4430,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -4453,7 +4453,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -4476,7 +4476,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -4522,7 +4522,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -4568,7 +4568,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -4591,7 +4591,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -4614,7 +4614,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -4637,7 +4637,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -4660,7 +4660,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -4683,7 +4683,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -4706,7 +4706,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -4729,7 +4729,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
@@ -4775,7 +4775,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -4798,7 +4798,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -4821,7 +4821,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -4844,7 +4844,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
@@ -4867,7 +4867,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
@@ -4913,7 +4913,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
@@ -4936,7 +4936,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -4959,7 +4959,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
@@ -4982,7 +4982,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
@@ -5028,7 +5028,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -5051,7 +5051,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -5097,7 +5097,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -5120,7 +5120,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -5143,7 +5143,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -5166,7 +5166,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
@@ -5189,7 +5189,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
@@ -5235,7 +5235,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -5281,7 +5281,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -5304,7 +5304,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -5327,7 +5327,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
@@ -5350,7 +5350,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -5373,7 +5373,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
@@ -5396,7 +5396,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -5442,7 +5442,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
@@ -5465,7 +5465,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
@@ -5488,7 +5488,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C198" t="n">
         <v>0</v>
@@ -5511,7 +5511,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C199" t="n">
         <v>0</v>
@@ -5534,7 +5534,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C200" t="n">
         <v>0</v>
@@ -5557,7 +5557,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C201" t="n">
         <v>0</v>
@@ -5580,7 +5580,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
@@ -5603,7 +5603,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C203" t="n">
         <v>0</v>
@@ -5626,7 +5626,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
@@ -5649,7 +5649,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C205" t="n">
         <v>0</v>
@@ -5672,7 +5672,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C206" t="n">
         <v>0</v>
@@ -5695,7 +5695,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C207" t="n">
         <v>0</v>
@@ -5718,7 +5718,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C208" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C209" t="n">
         <v>0</v>
@@ -5764,7 +5764,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C210" t="n">
         <v>0</v>
@@ -5787,7 +5787,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C211" t="n">
         <v>0</v>
@@ -5810,7 +5810,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C212" t="n">
         <v>0</v>
@@ -5833,7 +5833,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C213" t="n">
         <v>0</v>
@@ -5856,7 +5856,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C214" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C215" t="n">
         <v>0</v>
@@ -5902,7 +5902,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C216" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C217" t="n">
         <v>0</v>
@@ -5948,7 +5948,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C218" t="n">
         <v>0</v>
@@ -5971,7 +5971,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C219" t="n">
         <v>0</v>
@@ -5994,7 +5994,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C220" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C221" t="n">
         <v>0</v>
@@ -6040,7 +6040,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C222" t="n">
         <v>0</v>
@@ -6063,7 +6063,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C223" t="n">
         <v>0</v>
@@ -6086,7 +6086,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C224" t="n">
         <v>0</v>
@@ -6109,7 +6109,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C225" t="n">
         <v>0</v>
@@ -6132,7 +6132,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C226" t="n">
         <v>0</v>
@@ -6155,7 +6155,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C227" t="n">
         <v>0</v>
@@ -6178,7 +6178,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C228" t="n">
         <v>0</v>
@@ -6201,7 +6201,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C229" t="n">
         <v>0</v>
@@ -6224,7 +6224,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C230" t="n">
         <v>0</v>
@@ -6247,7 +6247,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C231" t="n">
         <v>0</v>
@@ -6270,7 +6270,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C232" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C233" t="n">
         <v>0</v>
@@ -6316,7 +6316,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C234" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C235" t="n">
         <v>0</v>
@@ -6362,7 +6362,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C236" t="n">
         <v>0</v>
@@ -6385,7 +6385,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C237" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C238" t="n">
         <v>0</v>
@@ -6431,7 +6431,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C239" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C240" t="n">
         <v>0</v>
@@ -6477,7 +6477,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C241" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C242" t="n">
         <v>0</v>
@@ -6523,7 +6523,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C243" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C244" t="n">
         <v>0</v>
@@ -6569,7 +6569,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C245" t="n">
         <v>0</v>
@@ -6592,7 +6592,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C246" t="n">
         <v>0</v>
@@ -6615,7 +6615,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C247" t="n">
         <v>0</v>
@@ -6638,7 +6638,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C248" t="n">
         <v>0</v>
@@ -6661,7 +6661,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C249" t="n">
         <v>0</v>
@@ -6684,7 +6684,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C250" t="n">
         <v>0</v>
@@ -6707,7 +6707,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C251" t="n">
         <v>0</v>
@@ -6730,7 +6730,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C252" t="n">
         <v>0</v>
@@ -6753,7 +6753,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C253" t="n">
         <v>0</v>
@@ -6776,7 +6776,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C254" t="n">
         <v>0</v>
@@ -6799,7 +6799,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C255" t="n">
         <v>0</v>
@@ -6822,7 +6822,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C256" t="n">
         <v>0</v>
@@ -6845,7 +6845,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C257" t="n">
         <v>0</v>
@@ -6868,7 +6868,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C258" t="n">
         <v>0</v>
@@ -6891,7 +6891,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C259" t="n">
         <v>0</v>
@@ -6914,7 +6914,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C260" t="n">
         <v>0</v>
@@ -6937,7 +6937,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C261" t="n">
         <v>0</v>
@@ -6960,7 +6960,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C262" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C263" t="n">
         <v>0</v>
@@ -7006,7 +7006,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C264" t="n">
         <v>0</v>
@@ -7029,7 +7029,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C265" t="n">
         <v>0</v>
@@ -7052,7 +7052,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C266" t="n">
         <v>0</v>
@@ -7075,7 +7075,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C267" t="n">
         <v>0</v>
@@ -7098,7 +7098,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C268" t="n">
         <v>0</v>
@@ -7121,7 +7121,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C269" t="n">
         <v>0</v>
@@ -7144,7 +7144,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C270" t="n">
         <v>0</v>
@@ -7167,7 +7167,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C271" t="n">
         <v>0</v>
@@ -7190,7 +7190,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C272" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C273" t="n">
         <v>0</v>
@@ -7236,7 +7236,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C274" t="n">
         <v>0</v>
@@ -7259,7 +7259,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C275" t="n">
         <v>0</v>
@@ -7282,7 +7282,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C276" t="n">
         <v>0</v>
@@ -7305,7 +7305,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C277" t="n">
         <v>0</v>
@@ -7328,7 +7328,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C278" t="n">
         <v>0</v>
@@ -7351,7 +7351,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C279" t="n">
         <v>0</v>
@@ -7374,7 +7374,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C280" t="n">
         <v>0</v>
@@ -7397,7 +7397,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C281" t="n">
         <v>0</v>
@@ -7420,7 +7420,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C282" t="n">
         <v>0</v>
@@ -7443,7 +7443,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C283" t="n">
         <v>0</v>
@@ -7466,7 +7466,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C284" t="n">
         <v>0</v>
@@ -7489,7 +7489,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C285" t="n">
         <v>0</v>
@@ -7512,7 +7512,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C286" t="n">
         <v>0</v>
@@ -7535,7 +7535,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C287" t="n">
         <v>0</v>
@@ -7558,7 +7558,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C288" t="n">
         <v>0</v>
@@ -7581,7 +7581,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C289" t="n">
         <v>0</v>
@@ -7604,7 +7604,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C290" t="n">
         <v>0</v>
@@ -7627,7 +7627,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C291" t="n">
         <v>0</v>
@@ -7650,7 +7650,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C292" t="n">
         <v>0</v>
@@ -7673,7 +7673,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C293" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C294" t="n">
         <v>0</v>
@@ -7719,7 +7719,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C295" t="n">
         <v>0</v>
@@ -7742,7 +7742,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C296" t="n">
         <v>0</v>
@@ -7765,7 +7765,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C297" t="n">
         <v>0</v>
@@ -7788,7 +7788,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C298" t="n">
         <v>0</v>
@@ -7811,7 +7811,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C299" t="n">
         <v>0</v>
@@ -7834,7 +7834,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C300" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C301" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C302" t="n">
         <v>0</v>
@@ -7903,7 +7903,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C303" t="n">
         <v>0</v>
@@ -7926,7 +7926,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C304" t="n">
         <v>0</v>
@@ -7949,7 +7949,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C305" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C306" t="n">
         <v>0</v>
@@ -7995,7 +7995,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C307" t="n">
         <v>0</v>
@@ -8018,7 +8018,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C308" t="n">
         <v>0</v>
@@ -8041,7 +8041,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C309" t="n">
         <v>0</v>
@@ -8064,7 +8064,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C310" t="n">
         <v>0</v>
@@ -8087,7 +8087,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C311" t="n">
         <v>0</v>
@@ -8110,7 +8110,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C312" t="n">
         <v>0</v>
@@ -8133,7 +8133,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C313" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C314" t="n">
         <v>0</v>
@@ -8179,7 +8179,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C315" t="n">
         <v>0</v>
@@ -8202,7 +8202,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="n">
-        <v>437.4174936111494</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C316" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C317" t="n">
         <v>0</v>
@@ -8248,7 +8248,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C318" t="n">
         <v>0</v>
@@ -8271,7 +8271,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C319" t="n">
         <v>0</v>
@@ -8294,7 +8294,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C320" t="n">
         <v>0</v>
@@ -8317,7 +8317,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C321" t="n">
         <v>0</v>
@@ -8340,7 +8340,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C322" t="n">
         <v>0</v>
@@ -8363,7 +8363,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C323" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C324" t="n">
         <v>0</v>
@@ -8409,7 +8409,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C325" t="n">
         <v>0</v>
@@ -8432,7 +8432,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C326" t="n">
         <v>0</v>
@@ -8455,7 +8455,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C327" t="n">
         <v>0</v>
@@ -8478,7 +8478,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C328" t="n">
         <v>0</v>
@@ -8501,7 +8501,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C329" t="n">
         <v>0</v>
@@ -8524,7 +8524,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C330" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="n">
-        <v>135.3813559322035</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C331" t="n">
         <v>0</v>
@@ -8570,7 +8570,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="n">
-        <v>135.3813559322035</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C332" t="n">
         <v>99.70783827229522</v>
@@ -8593,7 +8593,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="n">
-        <v>135.3813559322035</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C333" t="n">
         <v>99.70783827229522</v>
@@ -8616,7 +8616,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="n">
-        <v>135.3813559322035</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C334" t="n">
         <v>99.70783827229522</v>
@@ -8639,7 +8639,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="n">
-        <v>135.3813559322035</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C335" t="n">
         <v>99.70783827229522</v>
@@ -8662,7 +8662,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="n">
-        <v>135.3813559322035</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C336" t="n">
         <v>99.70783827229522</v>
@@ -8685,7 +8685,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="n">
-        <v>135.3813559322035</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C337" t="n">
         <v>99.70783827229522</v>
@@ -8708,7 +8708,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="n">
-        <v>135.3813559322035</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C338" t="n">
         <v>99.70783827229522</v>
@@ -8731,7 +8731,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="n">
-        <v>135.3813559322035</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C339" t="n">
         <v>99.70783827229522</v>
@@ -8754,7 +8754,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="n">
-        <v>135.3813559322035</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C340" t="n">
         <v>99.70783827229522</v>
@@ -8777,7 +8777,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="n">
-        <v>135.3813559322035</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C341" t="n">
         <v>99.70783827229522</v>
@@ -8800,7 +8800,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="n">
-        <v>135.3813559322035</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C342" t="n">
         <v>99.70783827229522</v>
@@ -8823,7 +8823,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="n">
-        <v>135.3813559322035</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C343" t="n">
         <v>99.70783827229522</v>
@@ -8846,7 +8846,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="n">
-        <v>135.3813559322035</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C344" t="n">
         <v>99.70783827229522</v>
@@ -8869,7 +8869,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="n">
-        <v>135.3813559322035</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C345" t="n">
         <v>99.70783827229522</v>
@@ -8892,7 +8892,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="n">
-        <v>135.3813559322035</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C346" t="n">
         <v>99.70783827229522</v>
@@ -8915,7 +8915,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C347" t="n">
         <v>99.70783827229522</v>
@@ -8938,7 +8938,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C348" t="n">
         <v>99.70783827229522</v>
@@ -8961,7 +8961,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C349" t="n">
         <v>99.70783827229522</v>
@@ -8984,7 +8984,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C350" t="n">
         <v>99.70783827229522</v>
@@ -9007,7 +9007,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C351" t="n">
         <v>99.70783827229522</v>
@@ -9030,7 +9030,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C352" t="n">
         <v>99.70783827229522</v>
@@ -9053,7 +9053,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C353" t="n">
         <v>99.70783827229522</v>
@@ -9076,7 +9076,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C354" t="n">
         <v>99.70783827229522</v>
@@ -9099,7 +9099,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C355" t="n">
         <v>99.70783827229522</v>
@@ -9122,7 +9122,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C356" t="n">
         <v>99.70783827229522</v>
@@ -9145,7 +9145,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C357" t="n">
         <v>99.70783827229522</v>
@@ -9168,7 +9168,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C358" t="n">
         <v>99.70783827229522</v>
@@ -9191,7 +9191,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C359" t="n">
         <v>99.70783827229522</v>
@@ -9214,7 +9214,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C360" t="n">
         <v>99.70783827229522</v>
@@ -9237,7 +9237,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C361" t="n">
         <v>99.70783827229522</v>
@@ -9260,7 +9260,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C362" t="n">
         <v>99.70783827229522</v>
@@ -9283,7 +9283,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C363" t="n">
         <v>99.70783827229522</v>
@@ -9306,7 +9306,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C364" t="n">
         <v>99.70783827229522</v>
@@ -9329,7 +9329,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C365" t="n">
         <v>99.70783827229522</v>
@@ -9352,7 +9352,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C366" t="n">
         <v>99.70783827229522</v>
@@ -9375,7 +9375,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C367" t="n">
         <v>99.70783827229522</v>
@@ -9398,7 +9398,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C368" t="n">
         <v>99.70783827229522</v>
@@ -9421,7 +9421,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C369" t="n">
         <v>99.70783827229522</v>
@@ -9444,7 +9444,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C370" t="n">
         <v>99.70783827229522</v>
@@ -9467,7 +9467,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C371" t="n">
         <v>99.70783827229522</v>
@@ -9490,7 +9490,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C372" t="n">
         <v>99.70783827229522</v>
@@ -9513,7 +9513,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C373" t="n">
         <v>99.70783827229522</v>
@@ -9536,7 +9536,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C374" t="n">
         <v>99.70783827229522</v>
@@ -9559,7 +9559,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C375" t="n">
         <v>99.70783827229522</v>
@@ -9582,7 +9582,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C376" t="n">
         <v>99.70783827229522</v>
@@ -9605,7 +9605,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C377" t="n">
         <v>99.70783827229522</v>
@@ -9628,7 +9628,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C378" t="n">
         <v>99.70783827229522</v>
@@ -9651,7 +9651,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C379" t="n">
         <v>99.70783827229522</v>
@@ -9674,7 +9674,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C380" t="n">
         <v>99.70783827229522</v>
@@ -9697,7 +9697,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C381" t="n">
         <v>99.70783827229522</v>
@@ -9720,7 +9720,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C382" t="n">
         <v>99.70783827229522</v>
@@ -9743,7 +9743,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C383" t="n">
         <v>99.70783827229522</v>
@@ -9766,7 +9766,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C384" t="n">
         <v>99.70783827229522</v>
@@ -9789,7 +9789,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C385" t="n">
         <v>99.70783827229522</v>
@@ -9812,7 +9812,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C386" t="n">
         <v>99.70783827229522</v>
@@ -9835,7 +9835,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C387" t="n">
         <v>99.70783827229522</v>
@@ -9858,7 +9858,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C388" t="n">
         <v>99.70783827229522</v>
@@ -9881,7 +9881,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C389" t="n">
         <v>99.70783827229522</v>
@@ -9904,7 +9904,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C390" t="n">
         <v>99.70783827229522</v>
@@ -9927,7 +9927,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="n">
-        <v>168.4349618508491</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C391" t="n">
         <v>99.70783827229522</v>
@@ -9950,7 +9950,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C392" t="n">
         <v>99.70783827229522</v>
@@ -9973,7 +9973,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C393" t="n">
         <v>99.70783827229522</v>
@@ -9996,7 +9996,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C394" t="n">
         <v>99.70783827229522</v>
@@ -10019,7 +10019,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C395" t="n">
         <v>99.70783827229522</v>
@@ -10042,7 +10042,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C396" t="n">
         <v>99.70783827229522</v>
@@ -10065,7 +10065,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C397" t="n">
         <v>99.70783827229522</v>
@@ -10088,7 +10088,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C398" t="n">
         <v>99.70783827229522</v>
@@ -10111,7 +10111,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C399" t="n">
         <v>99.70783827229522</v>
@@ -10134,7 +10134,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C400" t="n">
         <v>99.70783827229522</v>
@@ -10157,7 +10157,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C401" t="n">
         <v>99.70783827229522</v>
@@ -10180,7 +10180,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C402" t="n">
         <v>99.70783827229522</v>
@@ -10203,7 +10203,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C403" t="n">
         <v>99.70783827229522</v>
@@ -10226,7 +10226,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C404" t="n">
         <v>99.70783827229522</v>
@@ -10249,7 +10249,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C405" t="n">
         <v>99.70783827229522</v>
@@ -10272,7 +10272,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C406" t="n">
         <v>99.70783827229522</v>
@@ -10295,7 +10295,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C407" t="n">
         <v>99.70783827229522</v>
@@ -10318,7 +10318,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C408" t="n">
         <v>99.70783827229522</v>
@@ -10341,7 +10341,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C409" t="n">
         <v>99.70783827229522</v>
@@ -10364,7 +10364,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C410" t="n">
         <v>99.70783827229522</v>
@@ -10387,7 +10387,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C411" t="n">
         <v>99.70783827229522</v>
@@ -10410,7 +10410,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C412" t="n">
         <v>99.70783827229522</v>
@@ -10433,7 +10433,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C413" t="n">
         <v>99.70783827229522</v>
@@ -10456,7 +10456,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C414" t="n">
         <v>99.70783827229522</v>
@@ -10479,7 +10479,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C415" t="n">
         <v>99.70783827229522</v>
@@ -10502,7 +10502,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C416" t="n">
         <v>99.70783827229522</v>
@@ -10525,7 +10525,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C417" t="n">
         <v>99.70783827229522</v>
@@ -10548,7 +10548,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C418" t="n">
         <v>99.70783827229522</v>
@@ -10571,7 +10571,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C419" t="n">
         <v>99.70783827229522</v>
@@ -10594,7 +10594,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C420" t="n">
         <v>99.70783827229522</v>
@@ -10617,7 +10617,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C421" t="n">
         <v>99.70783827229522</v>
@@ -10640,7 +10640,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C422" t="n">
         <v>99.70783827229522</v>
@@ -10663,7 +10663,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C423" t="n">
         <v>99.70783827229522</v>
@@ -10686,7 +10686,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C424" t="n">
         <v>99.70783827229522</v>
@@ -10709,7 +10709,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C425" t="n">
         <v>99.70783827229522</v>
@@ -10732,7 +10732,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C426" t="n">
         <v>99.70783827229522</v>
@@ -10755,7 +10755,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C427" t="n">
         <v>99.70783827229522</v>
@@ -10778,7 +10778,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C428" t="n">
         <v>99.70783827229522</v>
@@ -10801,7 +10801,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C429" t="n">
         <v>99.70783827229522</v>
@@ -10824,7 +10824,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C430" t="n">
         <v>99.70783827229522</v>
@@ -10847,7 +10847,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C431" t="n">
         <v>99.70783827229522</v>
@@ -10870,7 +10870,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C432" t="n">
         <v>99.70783827229522</v>
@@ -10893,7 +10893,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C433" t="n">
         <v>99.70783827229522</v>
@@ -10916,7 +10916,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C434" t="n">
         <v>99.70783827229522</v>
@@ -10939,7 +10939,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C435" t="n">
         <v>99.70783827229522</v>
@@ -10962,7 +10962,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="n">
-        <v>0</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C436" t="n">
         <v>99.70783827229522</v>
@@ -10985,7 +10985,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C437" t="n">
         <v>99.70783827229522</v>
@@ -11008,7 +11008,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C438" t="n">
         <v>99.70783827229522</v>
@@ -11031,7 +11031,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C439" t="n">
         <v>99.70783827229522</v>
@@ -11054,7 +11054,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C440" t="n">
         <v>99.70783827229522</v>
@@ -11077,7 +11077,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C441" t="n">
         <v>99.70783827229522</v>
@@ -11100,7 +11100,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C442" t="n">
         <v>99.70783827229522</v>
@@ -11123,7 +11123,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C443" t="n">
         <v>99.70783827229522</v>
@@ -11146,7 +11146,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C444" t="n">
         <v>99.70783827229522</v>
@@ -11169,7 +11169,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C445" t="n">
         <v>99.70783827229522</v>
@@ -11192,7 +11192,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C446" t="n">
         <v>99.70783827229522</v>
@@ -11215,7 +11215,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C447" t="n">
         <v>99.70783827229522</v>
@@ -11238,7 +11238,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C448" t="n">
         <v>99.70783827229522</v>
@@ -11261,7 +11261,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C449" t="n">
         <v>99.70783827229522</v>
@@ -11284,7 +11284,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C450" t="n">
         <v>99.70783827229522</v>
@@ -11307,7 +11307,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C451" t="n">
         <v>99.70783827229522</v>
@@ -11330,7 +11330,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C452" t="n">
         <v>99.70783827229522</v>
@@ -11353,7 +11353,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C453" t="n">
         <v>99.70783827229522</v>
@@ -11376,7 +11376,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C454" t="n">
         <v>99.70783827229522</v>
@@ -11399,7 +11399,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C455" t="n">
         <v>99.70783827229522</v>
@@ -11422,7 +11422,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C456" t="n">
         <v>99.70783827229522</v>
@@ -11445,7 +11445,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C457" t="n">
         <v>99.70783827229522</v>
@@ -11468,7 +11468,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C458" t="n">
         <v>99.70783827229522</v>
@@ -11491,7 +11491,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C459" t="n">
         <v>99.70783827229522</v>
@@ -11514,7 +11514,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C460" t="n">
         <v>99.70783827229522</v>
@@ -11537,7 +11537,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C461" t="n">
         <v>99.70783827229522</v>
@@ -11560,7 +11560,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C462" t="n">
         <v>99.70783827229522</v>
@@ -11583,7 +11583,7 @@
         <v>461</v>
       </c>
       <c r="B463" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C463" t="n">
         <v>99.70783827229522</v>
@@ -11606,7 +11606,7 @@
         <v>462</v>
       </c>
       <c r="B464" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C464" t="n">
         <v>99.70783827229522</v>
@@ -11629,7 +11629,7 @@
         <v>463</v>
       </c>
       <c r="B465" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C465" t="n">
         <v>99.70783827229522</v>
@@ -11652,7 +11652,7 @@
         <v>464</v>
       </c>
       <c r="B466" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C466" t="n">
         <v>99.70783827229522</v>
@@ -11675,7 +11675,7 @@
         <v>465</v>
       </c>
       <c r="B467" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C467" t="n">
         <v>99.70783827229522</v>
@@ -11698,7 +11698,7 @@
         <v>466</v>
       </c>
       <c r="B468" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C468" t="n">
         <v>99.70783827229522</v>
@@ -11721,7 +11721,7 @@
         <v>467</v>
       </c>
       <c r="B469" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C469" t="n">
         <v>99.70783827229522</v>
@@ -11744,7 +11744,7 @@
         <v>468</v>
       </c>
       <c r="B470" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C470" t="n">
         <v>99.70783827229522</v>
@@ -11767,7 +11767,7 @@
         <v>469</v>
       </c>
       <c r="B471" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C471" t="n">
         <v>99.70783827229522</v>
@@ -11790,7 +11790,7 @@
         <v>470</v>
       </c>
       <c r="B472" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C472" t="n">
         <v>99.70783827229522</v>
@@ -11813,7 +11813,7 @@
         <v>471</v>
       </c>
       <c r="B473" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C473" t="n">
         <v>99.70783827229522</v>
@@ -11836,7 +11836,7 @@
         <v>472</v>
       </c>
       <c r="B474" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C474" t="n">
         <v>99.70783827229522</v>
@@ -11859,7 +11859,7 @@
         <v>473</v>
       </c>
       <c r="B475" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C475" t="n">
         <v>99.70783827229522</v>
@@ -11882,7 +11882,7 @@
         <v>474</v>
       </c>
       <c r="B476" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C476" t="n">
         <v>99.70783827229522</v>
@@ -11905,7 +11905,7 @@
         <v>475</v>
       </c>
       <c r="B477" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C477" t="n">
         <v>99.70783827229522</v>
@@ -11928,7 +11928,7 @@
         <v>476</v>
       </c>
       <c r="B478" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C478" t="n">
         <v>99.70783827229522</v>
@@ -11951,7 +11951,7 @@
         <v>477</v>
       </c>
       <c r="B479" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C479" t="n">
         <v>99.70783827229522</v>
@@ -11974,7 +11974,7 @@
         <v>478</v>
       </c>
       <c r="B480" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C480" t="n">
         <v>99.70783827229522</v>
@@ -11997,7 +11997,7 @@
         <v>479</v>
       </c>
       <c r="B481" t="n">
-        <v>165.3763828763829</v>
+        <v>575.487296200834</v>
       </c>
       <c r="C481" t="n">
         <v>99.70783827229522</v>
@@ -28902,7 +28902,7 @@
         <v>1214</v>
       </c>
       <c r="B1216" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1216" t="n">
         <v>104.6947853884265</v>
@@ -28925,7 +28925,7 @@
         <v>1215</v>
       </c>
       <c r="B1217" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1217" t="n">
         <v>104.6947853884265</v>
@@ -28948,7 +28948,7 @@
         <v>1216</v>
       </c>
       <c r="B1218" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1218" t="n">
         <v>104.6947853884265</v>
@@ -28971,7 +28971,7 @@
         <v>1217</v>
       </c>
       <c r="B1219" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1219" t="n">
         <v>104.6947853884265</v>
@@ -28994,7 +28994,7 @@
         <v>1218</v>
       </c>
       <c r="B1220" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1220" t="n">
         <v>104.6947853884265</v>
@@ -29017,7 +29017,7 @@
         <v>1219</v>
       </c>
       <c r="B1221" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1221" t="n">
         <v>104.6947853884265</v>
@@ -29040,7 +29040,7 @@
         <v>1220</v>
       </c>
       <c r="B1222" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1222" t="n">
         <v>104.6947853884265</v>
@@ -29063,7 +29063,7 @@
         <v>1221</v>
       </c>
       <c r="B1223" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1223" t="n">
         <v>104.6947853884265</v>
@@ -29086,7 +29086,7 @@
         <v>1222</v>
       </c>
       <c r="B1224" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1224" t="n">
         <v>104.6947853884265</v>
@@ -29109,7 +29109,7 @@
         <v>1223</v>
       </c>
       <c r="B1225" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1225" t="n">
         <v>104.6947853884265</v>
@@ -29132,7 +29132,7 @@
         <v>1224</v>
       </c>
       <c r="B1226" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1226" t="n">
         <v>104.6947853884265</v>
@@ -29155,7 +29155,7 @@
         <v>1225</v>
       </c>
       <c r="B1227" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1227" t="n">
         <v>104.6947853884265</v>
@@ -29178,7 +29178,7 @@
         <v>1226</v>
       </c>
       <c r="B1228" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1228" t="n">
         <v>104.6947853884265</v>
@@ -29201,7 +29201,7 @@
         <v>1227</v>
       </c>
       <c r="B1229" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1229" t="n">
         <v>104.6947853884265</v>
@@ -29224,7 +29224,7 @@
         <v>1228</v>
       </c>
       <c r="B1230" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1230" t="n">
         <v>104.6947853884265</v>
@@ -29247,7 +29247,7 @@
         <v>1229</v>
       </c>
       <c r="B1231" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1231" t="n">
         <v>104.6947853884265</v>
@@ -29270,7 +29270,7 @@
         <v>1230</v>
       </c>
       <c r="B1232" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1232" t="n">
         <v>104.6947853884265</v>
@@ -29293,7 +29293,7 @@
         <v>1231</v>
       </c>
       <c r="B1233" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1233" t="n">
         <v>104.6947853884265</v>
@@ -29316,7 +29316,7 @@
         <v>1232</v>
       </c>
       <c r="B1234" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1234" t="n">
         <v>104.6947853884265</v>
@@ -29339,7 +29339,7 @@
         <v>1233</v>
       </c>
       <c r="B1235" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1235" t="n">
         <v>104.6947853884265</v>
@@ -29362,7 +29362,7 @@
         <v>1234</v>
       </c>
       <c r="B1236" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1236" t="n">
         <v>104.6947853884265</v>
@@ -29385,7 +29385,7 @@
         <v>1235</v>
       </c>
       <c r="B1237" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1237" t="n">
         <v>104.6947853884265</v>
@@ -29408,7 +29408,7 @@
         <v>1236</v>
       </c>
       <c r="B1238" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1238" t="n">
         <v>104.6947853884265</v>
@@ -29431,7 +29431,7 @@
         <v>1237</v>
       </c>
       <c r="B1239" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1239" t="n">
         <v>104.6947853884265</v>
@@ -29454,7 +29454,7 @@
         <v>1238</v>
       </c>
       <c r="B1240" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1240" t="n">
         <v>104.6947853884265</v>
@@ -29477,7 +29477,7 @@
         <v>1239</v>
       </c>
       <c r="B1241" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1241" t="n">
         <v>104.6947853884265</v>
@@ -29500,7 +29500,7 @@
         <v>1240</v>
       </c>
       <c r="B1242" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1242" t="n">
         <v>104.6947853884265</v>
@@ -29523,7 +29523,7 @@
         <v>1241</v>
       </c>
       <c r="B1243" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1243" t="n">
         <v>104.6947853884265</v>
@@ -29546,7 +29546,7 @@
         <v>1242</v>
       </c>
       <c r="B1244" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1244" t="n">
         <v>104.6947853884265</v>
@@ -29569,7 +29569,7 @@
         <v>1243</v>
       </c>
       <c r="B1245" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1245" t="n">
         <v>104.6947853884265</v>
@@ -29592,7 +29592,7 @@
         <v>1244</v>
       </c>
       <c r="B1246" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1246" t="n">
         <v>104.6947853884265</v>
@@ -29615,7 +29615,7 @@
         <v>1245</v>
       </c>
       <c r="B1247" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1247" t="n">
         <v>104.6947853884265</v>
@@ -29638,7 +29638,7 @@
         <v>1246</v>
       </c>
       <c r="B1248" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1248" t="n">
         <v>104.6947853884265</v>
@@ -29661,7 +29661,7 @@
         <v>1247</v>
       </c>
       <c r="B1249" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1249" t="n">
         <v>104.6947853884265</v>
@@ -29684,7 +29684,7 @@
         <v>1248</v>
       </c>
       <c r="B1250" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1250" t="n">
         <v>104.6947853884265</v>
@@ -29707,7 +29707,7 @@
         <v>1249</v>
       </c>
       <c r="B1251" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1251" t="n">
         <v>104.6947853884265</v>
@@ -29730,7 +29730,7 @@
         <v>1250</v>
       </c>
       <c r="B1252" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1252" t="n">
         <v>104.6947853884265</v>
@@ -29753,7 +29753,7 @@
         <v>1251</v>
       </c>
       <c r="B1253" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1253" t="n">
         <v>104.6947853884265</v>
@@ -29776,7 +29776,7 @@
         <v>1252</v>
       </c>
       <c r="B1254" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1254" t="n">
         <v>104.6947853884265</v>
@@ -29799,7 +29799,7 @@
         <v>1253</v>
       </c>
       <c r="B1255" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1255" t="n">
         <v>104.6947853884265</v>
@@ -29822,7 +29822,7 @@
         <v>1254</v>
       </c>
       <c r="B1256" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1256" t="n">
         <v>104.6947853884265</v>
@@ -29845,7 +29845,7 @@
         <v>1255</v>
       </c>
       <c r="B1257" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1257" t="n">
         <v>104.6947853884265</v>
@@ -29868,7 +29868,7 @@
         <v>1256</v>
       </c>
       <c r="B1258" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1258" t="n">
         <v>104.6947853884265</v>
@@ -29891,7 +29891,7 @@
         <v>1257</v>
       </c>
       <c r="B1259" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1259" t="n">
         <v>104.6947853884265</v>
@@ -29914,7 +29914,7 @@
         <v>1258</v>
       </c>
       <c r="B1260" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1260" t="n">
         <v>104.6947853884265</v>
@@ -29937,7 +29937,7 @@
         <v>1259</v>
       </c>
       <c r="B1261" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1261" t="n">
         <v>104.6947853884265</v>
@@ -29960,7 +29960,7 @@
         <v>1260</v>
       </c>
       <c r="B1262" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1262" t="n">
         <v>104.6947853884265</v>
@@ -29983,7 +29983,7 @@
         <v>1261</v>
       </c>
       <c r="B1263" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1263" t="n">
         <v>104.6947853884265</v>
@@ -30006,7 +30006,7 @@
         <v>1262</v>
       </c>
       <c r="B1264" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1264" t="n">
         <v>104.6947853884265</v>
@@ -30029,7 +30029,7 @@
         <v>1263</v>
       </c>
       <c r="B1265" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1265" t="n">
         <v>104.6947853884265</v>
@@ -30052,7 +30052,7 @@
         <v>1264</v>
       </c>
       <c r="B1266" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1266" t="n">
         <v>104.6947853884265</v>
@@ -30075,7 +30075,7 @@
         <v>1265</v>
       </c>
       <c r="B1267" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1267" t="n">
         <v>104.6947853884265</v>
@@ -30098,7 +30098,7 @@
         <v>1266</v>
       </c>
       <c r="B1268" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1268" t="n">
         <v>104.6947853884265</v>
@@ -30121,7 +30121,7 @@
         <v>1267</v>
       </c>
       <c r="B1269" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1269" t="n">
         <v>104.6947853884265</v>
@@ -30144,7 +30144,7 @@
         <v>1268</v>
       </c>
       <c r="B1270" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1270" t="n">
         <v>104.6947853884265</v>
@@ -30167,7 +30167,7 @@
         <v>1269</v>
       </c>
       <c r="B1271" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1271" t="n">
         <v>104.6947853884265</v>
@@ -30190,7 +30190,7 @@
         <v>1270</v>
       </c>
       <c r="B1272" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1272" t="n">
         <v>104.6947853884265</v>
@@ -30213,7 +30213,7 @@
         <v>1271</v>
       </c>
       <c r="B1273" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1273" t="n">
         <v>104.6947853884265</v>
@@ -30236,7 +30236,7 @@
         <v>1272</v>
       </c>
       <c r="B1274" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1274" t="n">
         <v>104.6947853884265</v>
@@ -30259,7 +30259,7 @@
         <v>1273</v>
       </c>
       <c r="B1275" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1275" t="n">
         <v>104.6947853884265</v>
@@ -30282,7 +30282,7 @@
         <v>1274</v>
       </c>
       <c r="B1276" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1276" t="n">
         <v>104.6947853884265</v>
@@ -30305,7 +30305,7 @@
         <v>1275</v>
       </c>
       <c r="B1277" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1277" t="n">
         <v>104.6947853884265</v>
@@ -30328,7 +30328,7 @@
         <v>1276</v>
       </c>
       <c r="B1278" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1278" t="n">
         <v>104.6947853884265</v>
@@ -30351,7 +30351,7 @@
         <v>1277</v>
       </c>
       <c r="B1279" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1279" t="n">
         <v>104.6947853884265</v>
@@ -30374,7 +30374,7 @@
         <v>1278</v>
       </c>
       <c r="B1280" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1280" t="n">
         <v>104.6947853884265</v>
@@ -30397,7 +30397,7 @@
         <v>1279</v>
       </c>
       <c r="B1281" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1281" t="n">
         <v>104.6947853884265</v>
@@ -30420,7 +30420,7 @@
         <v>1280</v>
       </c>
       <c r="B1282" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1282" t="n">
         <v>104.6947853884265</v>
@@ -30443,7 +30443,7 @@
         <v>1281</v>
       </c>
       <c r="B1283" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1283" t="n">
         <v>104.6947853884265</v>
@@ -30466,7 +30466,7 @@
         <v>1282</v>
       </c>
       <c r="B1284" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1284" t="n">
         <v>104.6947853884265</v>
@@ -30489,7 +30489,7 @@
         <v>1283</v>
       </c>
       <c r="B1285" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1285" t="n">
         <v>104.6947853884265</v>
@@ -30512,7 +30512,7 @@
         <v>1284</v>
       </c>
       <c r="B1286" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1286" t="n">
         <v>104.6947853884265</v>
@@ -30535,7 +30535,7 @@
         <v>1285</v>
       </c>
       <c r="B1287" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1287" t="n">
         <v>104.6947853884265</v>
@@ -30558,7 +30558,7 @@
         <v>1286</v>
       </c>
       <c r="B1288" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1288" t="n">
         <v>104.6947853884265</v>
@@ -30581,7 +30581,7 @@
         <v>1287</v>
       </c>
       <c r="B1289" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1289" t="n">
         <v>104.6947853884265</v>
@@ -30604,7 +30604,7 @@
         <v>1288</v>
       </c>
       <c r="B1290" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1290" t="n">
         <v>104.6947853884265</v>
@@ -30627,7 +30627,7 @@
         <v>1289</v>
       </c>
       <c r="B1291" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1291" t="n">
         <v>104.6947853884265</v>
@@ -30650,7 +30650,7 @@
         <v>1290</v>
       </c>
       <c r="B1292" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1292" t="n">
         <v>104.6947853884265</v>
@@ -30673,7 +30673,7 @@
         <v>1291</v>
       </c>
       <c r="B1293" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1293" t="n">
         <v>104.6947853884265</v>
@@ -30696,7 +30696,7 @@
         <v>1292</v>
       </c>
       <c r="B1294" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1294" t="n">
         <v>104.6947853884265</v>
@@ -30719,7 +30719,7 @@
         <v>1293</v>
       </c>
       <c r="B1295" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1295" t="n">
         <v>104.6947853884265</v>
@@ -30742,7 +30742,7 @@
         <v>1294</v>
       </c>
       <c r="B1296" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1296" t="n">
         <v>104.6947853884265</v>
@@ -30765,7 +30765,7 @@
         <v>1295</v>
       </c>
       <c r="B1297" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1297" t="n">
         <v>104.6947853884265</v>
@@ -30788,7 +30788,7 @@
         <v>1296</v>
       </c>
       <c r="B1298" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1298" t="n">
         <v>104.6947853884265</v>
@@ -30811,7 +30811,7 @@
         <v>1297</v>
       </c>
       <c r="B1299" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1299" t="n">
         <v>104.6947853884265</v>
@@ -30834,7 +30834,7 @@
         <v>1298</v>
       </c>
       <c r="B1300" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1300" t="n">
         <v>104.6947853884265</v>
@@ -30857,7 +30857,7 @@
         <v>1299</v>
       </c>
       <c r="B1301" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1301" t="n">
         <v>104.6947853884265</v>
@@ -30880,7 +30880,7 @@
         <v>1300</v>
       </c>
       <c r="B1302" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1302" t="n">
         <v>104.6947853884265</v>
@@ -30903,7 +30903,7 @@
         <v>1301</v>
       </c>
       <c r="B1303" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1303" t="n">
         <v>104.6947853884265</v>
@@ -30926,7 +30926,7 @@
         <v>1302</v>
       </c>
       <c r="B1304" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1304" t="n">
         <v>104.6947853884265</v>
@@ -30949,7 +30949,7 @@
         <v>1303</v>
       </c>
       <c r="B1305" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1305" t="n">
         <v>104.6947853884265</v>
@@ -30972,7 +30972,7 @@
         <v>1304</v>
       </c>
       <c r="B1306" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1306" t="n">
         <v>104.6947853884265</v>
@@ -30995,7 +30995,7 @@
         <v>1305</v>
       </c>
       <c r="B1307" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1307" t="n">
         <v>104.6947853884265</v>
@@ -31018,7 +31018,7 @@
         <v>1306</v>
       </c>
       <c r="B1308" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1308" t="n">
         <v>104.6947853884265</v>
@@ -31041,7 +31041,7 @@
         <v>1307</v>
       </c>
       <c r="B1309" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1309" t="n">
         <v>104.6947853884265</v>
@@ -31064,7 +31064,7 @@
         <v>1308</v>
       </c>
       <c r="B1310" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1310" t="n">
         <v>104.6947853884265</v>
@@ -31087,7 +31087,7 @@
         <v>1309</v>
       </c>
       <c r="B1311" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1311" t="n">
         <v>104.6947853884265</v>
@@ -31110,7 +31110,7 @@
         <v>1310</v>
       </c>
       <c r="B1312" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1312" t="n">
         <v>104.6947853884265</v>
@@ -31133,7 +31133,7 @@
         <v>1311</v>
       </c>
       <c r="B1313" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1313" t="n">
         <v>104.6947853884265</v>
@@ -31156,7 +31156,7 @@
         <v>1312</v>
       </c>
       <c r="B1314" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1314" t="n">
         <v>104.6947853884265</v>
@@ -31179,7 +31179,7 @@
         <v>1313</v>
       </c>
       <c r="B1315" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1315" t="n">
         <v>104.6947853884265</v>
@@ -31202,7 +31202,7 @@
         <v>1314</v>
       </c>
       <c r="B1316" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1316" t="n">
         <v>104.6947853884265</v>
@@ -31225,7 +31225,7 @@
         <v>1315</v>
       </c>
       <c r="B1317" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1317" t="n">
         <v>104.6947853884265</v>
@@ -31248,7 +31248,7 @@
         <v>1316</v>
       </c>
       <c r="B1318" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1318" t="n">
         <v>104.6947853884265</v>
@@ -31271,7 +31271,7 @@
         <v>1317</v>
       </c>
       <c r="B1319" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1319" t="n">
         <v>104.6947853884265</v>
@@ -31294,7 +31294,7 @@
         <v>1318</v>
       </c>
       <c r="B1320" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1320" t="n">
         <v>104.6947853884265</v>
@@ -31317,7 +31317,7 @@
         <v>1319</v>
       </c>
       <c r="B1321" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1321" t="n">
         <v>104.6947853884265</v>
@@ -31340,7 +31340,7 @@
         <v>1320</v>
       </c>
       <c r="B1322" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1322" t="n">
         <v>104.6947853884265</v>
@@ -31363,7 +31363,7 @@
         <v>1321</v>
       </c>
       <c r="B1323" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1323" t="n">
         <v>104.6947853884265</v>
@@ -31386,7 +31386,7 @@
         <v>1322</v>
       </c>
       <c r="B1324" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1324" t="n">
         <v>104.6947853884265</v>
@@ -31409,7 +31409,7 @@
         <v>1323</v>
       </c>
       <c r="B1325" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1325" t="n">
         <v>104.6947853884265</v>
@@ -31432,7 +31432,7 @@
         <v>1324</v>
       </c>
       <c r="B1326" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1326" t="n">
         <v>104.6947853884265</v>
@@ -31455,7 +31455,7 @@
         <v>1325</v>
       </c>
       <c r="B1327" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1327" t="n">
         <v>104.6947853884265</v>
@@ -31478,7 +31478,7 @@
         <v>1326</v>
       </c>
       <c r="B1328" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1328" t="n">
         <v>104.6947853884265</v>
@@ -31501,7 +31501,7 @@
         <v>1327</v>
       </c>
       <c r="B1329" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1329" t="n">
         <v>104.6947853884265</v>
@@ -31524,7 +31524,7 @@
         <v>1328</v>
       </c>
       <c r="B1330" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1330" t="n">
         <v>104.6947853884265</v>
@@ -31547,7 +31547,7 @@
         <v>1329</v>
       </c>
       <c r="B1331" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1331" t="n">
         <v>104.6947853884265</v>
@@ -31570,7 +31570,7 @@
         <v>1330</v>
       </c>
       <c r="B1332" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1332" t="n">
         <v>104.6947853884265</v>
@@ -31593,7 +31593,7 @@
         <v>1331</v>
       </c>
       <c r="B1333" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1333" t="n">
         <v>104.6947853884265</v>
@@ -31616,7 +31616,7 @@
         <v>1332</v>
       </c>
       <c r="B1334" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1334" t="n">
         <v>104.6947853884265</v>
@@ -31639,7 +31639,7 @@
         <v>1333</v>
       </c>
       <c r="B1335" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1335" t="n">
         <v>104.6947853884265</v>
@@ -31662,7 +31662,7 @@
         <v>1334</v>
       </c>
       <c r="B1336" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1336" t="n">
         <v>104.6947853884265</v>
@@ -31685,7 +31685,7 @@
         <v>1335</v>
       </c>
       <c r="B1337" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1337" t="n">
         <v>104.6947853884265</v>
@@ -31708,7 +31708,7 @@
         <v>1336</v>
       </c>
       <c r="B1338" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1338" t="n">
         <v>104.6947853884265</v>
@@ -31731,7 +31731,7 @@
         <v>1337</v>
       </c>
       <c r="B1339" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1339" t="n">
         <v>104.6947853884265</v>
@@ -31754,7 +31754,7 @@
         <v>1338</v>
       </c>
       <c r="B1340" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1340" t="n">
         <v>104.6947853884265</v>
@@ -31777,7 +31777,7 @@
         <v>1339</v>
       </c>
       <c r="B1341" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1341" t="n">
         <v>104.6947853884265</v>
@@ -31800,7 +31800,7 @@
         <v>1340</v>
       </c>
       <c r="B1342" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1342" t="n">
         <v>104.6947853884265</v>
@@ -31823,7 +31823,7 @@
         <v>1341</v>
       </c>
       <c r="B1343" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1343" t="n">
         <v>104.6947853884265</v>
@@ -31846,7 +31846,7 @@
         <v>1342</v>
       </c>
       <c r="B1344" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1344" t="n">
         <v>104.6947853884265</v>
@@ -31869,7 +31869,7 @@
         <v>1343</v>
       </c>
       <c r="B1345" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1345" t="n">
         <v>104.6947853884265</v>
@@ -31892,7 +31892,7 @@
         <v>1344</v>
       </c>
       <c r="B1346" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1346" t="n">
         <v>104.6947853884265</v>
@@ -31915,7 +31915,7 @@
         <v>1345</v>
       </c>
       <c r="B1347" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1347" t="n">
         <v>104.6947853884265</v>
@@ -31938,7 +31938,7 @@
         <v>1346</v>
       </c>
       <c r="B1348" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1348" t="n">
         <v>104.6947853884265</v>
@@ -31961,7 +31961,7 @@
         <v>1347</v>
       </c>
       <c r="B1349" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1349" t="n">
         <v>104.6947853884265</v>
@@ -31984,7 +31984,7 @@
         <v>1348</v>
       </c>
       <c r="B1350" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1350" t="n">
         <v>104.6947853884265</v>
@@ -32007,7 +32007,7 @@
         <v>1349</v>
       </c>
       <c r="B1351" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1351" t="n">
         <v>104.6947853884265</v>
@@ -32030,7 +32030,7 @@
         <v>1350</v>
       </c>
       <c r="B1352" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1352" t="n">
         <v>104.6947853884265</v>
@@ -32053,7 +32053,7 @@
         <v>1351</v>
       </c>
       <c r="B1353" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1353" t="n">
         <v>104.6947853884265</v>
@@ -32076,7 +32076,7 @@
         <v>1352</v>
       </c>
       <c r="B1354" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1354" t="n">
         <v>104.6947853884265</v>
@@ -32099,7 +32099,7 @@
         <v>1353</v>
       </c>
       <c r="B1355" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1355" t="n">
         <v>104.6947853884265</v>
@@ -32122,7 +32122,7 @@
         <v>1354</v>
       </c>
       <c r="B1356" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1356" t="n">
         <v>104.6947853884265</v>
@@ -32145,7 +32145,7 @@
         <v>1355</v>
       </c>
       <c r="B1357" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1357" t="n">
         <v>104.6947853884265</v>
@@ -32168,7 +32168,7 @@
         <v>1356</v>
       </c>
       <c r="B1358" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1358" t="n">
         <v>104.6947853884265</v>
@@ -32191,7 +32191,7 @@
         <v>1357</v>
       </c>
       <c r="B1359" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1359" t="n">
         <v>104.6947853884265</v>
@@ -32214,7 +32214,7 @@
         <v>1358</v>
       </c>
       <c r="B1360" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1360" t="n">
         <v>104.6947853884265</v>
@@ -32237,7 +32237,7 @@
         <v>1359</v>
       </c>
       <c r="B1361" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1361" t="n">
         <v>104.6947853884265</v>
@@ -32260,7 +32260,7 @@
         <v>1360</v>
       </c>
       <c r="B1362" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1362" t="n">
         <v>104.6947853884265</v>
@@ -32283,7 +32283,7 @@
         <v>1361</v>
       </c>
       <c r="B1363" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1363" t="n">
         <v>104.6947853884265</v>
@@ -32306,7 +32306,7 @@
         <v>1362</v>
       </c>
       <c r="B1364" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1364" t="n">
         <v>104.6947853884265</v>
@@ -32329,7 +32329,7 @@
         <v>1363</v>
       </c>
       <c r="B1365" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1365" t="n">
         <v>104.6947853884265</v>
@@ -32352,7 +32352,7 @@
         <v>1364</v>
       </c>
       <c r="B1366" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1366" t="n">
         <v>104.6947853884265</v>
@@ -32375,7 +32375,7 @@
         <v>1365</v>
       </c>
       <c r="B1367" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1367" t="n">
         <v>104.6947853884265</v>
@@ -32398,7 +32398,7 @@
         <v>1366</v>
       </c>
       <c r="B1368" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1368" t="n">
         <v>104.6947853884265</v>
@@ -32421,7 +32421,7 @@
         <v>1367</v>
       </c>
       <c r="B1369" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1369" t="n">
         <v>104.6947853884265</v>
@@ -32444,7 +32444,7 @@
         <v>1368</v>
       </c>
       <c r="B1370" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1370" t="n">
         <v>104.6947853884265</v>
@@ -32467,7 +32467,7 @@
         <v>1369</v>
       </c>
       <c r="B1371" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1371" t="n">
         <v>104.6947853884265</v>
@@ -32490,7 +32490,7 @@
         <v>1370</v>
       </c>
       <c r="B1372" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1372" t="n">
         <v>104.6947853884265</v>
@@ -32513,7 +32513,7 @@
         <v>1371</v>
       </c>
       <c r="B1373" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1373" t="n">
         <v>104.6947853884265</v>
@@ -32536,7 +32536,7 @@
         <v>1372</v>
       </c>
       <c r="B1374" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1374" t="n">
         <v>104.6947853884265</v>
@@ -32559,7 +32559,7 @@
         <v>1373</v>
       </c>
       <c r="B1375" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1375" t="n">
         <v>104.6947853884265</v>
@@ -32582,7 +32582,7 @@
         <v>1374</v>
       </c>
       <c r="B1376" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1376" t="n">
         <v>104.6947853884265</v>
@@ -32605,7 +32605,7 @@
         <v>1375</v>
       </c>
       <c r="B1377" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1377" t="n">
         <v>104.6947853884265</v>
@@ -32628,7 +32628,7 @@
         <v>1376</v>
       </c>
       <c r="B1378" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1378" t="n">
         <v>104.6947853884265</v>
@@ -32651,7 +32651,7 @@
         <v>1377</v>
       </c>
       <c r="B1379" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1379" t="n">
         <v>104.6947853884265</v>
@@ -32674,7 +32674,7 @@
         <v>1378</v>
       </c>
       <c r="B1380" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1380" t="n">
         <v>104.6947853884265</v>
@@ -32697,7 +32697,7 @@
         <v>1379</v>
       </c>
       <c r="B1381" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1381" t="n">
         <v>104.6947853884265</v>
@@ -32720,7 +32720,7 @@
         <v>1380</v>
       </c>
       <c r="B1382" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1382" t="n">
         <v>104.6947853884265</v>
@@ -32743,7 +32743,7 @@
         <v>1381</v>
       </c>
       <c r="B1383" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1383" t="n">
         <v>104.6947853884265</v>
@@ -32766,7 +32766,7 @@
         <v>1382</v>
       </c>
       <c r="B1384" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1384" t="n">
         <v>104.6947853884265</v>
@@ -32789,7 +32789,7 @@
         <v>1383</v>
       </c>
       <c r="B1385" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1385" t="n">
         <v>104.6947853884265</v>
@@ -32812,7 +32812,7 @@
         <v>1384</v>
       </c>
       <c r="B1386" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1386" t="n">
         <v>104.6947853884265</v>
@@ -32835,7 +32835,7 @@
         <v>1385</v>
       </c>
       <c r="B1387" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1387" t="n">
         <v>104.6947853884265</v>
@@ -32858,7 +32858,7 @@
         <v>1386</v>
       </c>
       <c r="B1388" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1388" t="n">
         <v>104.6947853884265</v>
@@ -32881,7 +32881,7 @@
         <v>1387</v>
       </c>
       <c r="B1389" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1389" t="n">
         <v>104.6947853884265</v>
@@ -32904,7 +32904,7 @@
         <v>1388</v>
       </c>
       <c r="B1390" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1390" t="n">
         <v>104.6947853884265</v>
@@ -32927,7 +32927,7 @@
         <v>1389</v>
       </c>
       <c r="B1391" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1391" t="n">
         <v>104.6947853884265</v>
@@ -32950,7 +32950,7 @@
         <v>1390</v>
       </c>
       <c r="B1392" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1392" t="n">
         <v>104.6947853884265</v>
@@ -32973,7 +32973,7 @@
         <v>1391</v>
       </c>
       <c r="B1393" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1393" t="n">
         <v>104.6947853884265</v>
@@ -32996,7 +32996,7 @@
         <v>1392</v>
       </c>
       <c r="B1394" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1394" t="n">
         <v>104.6947853884265</v>
@@ -33019,7 +33019,7 @@
         <v>1393</v>
       </c>
       <c r="B1395" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1395" t="n">
         <v>104.6947853884265</v>
@@ -33042,7 +33042,7 @@
         <v>1394</v>
       </c>
       <c r="B1396" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1396" t="n">
         <v>104.6947853884265</v>
@@ -33065,7 +33065,7 @@
         <v>1395</v>
       </c>
       <c r="B1397" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1397" t="n">
         <v>0</v>
@@ -33088,7 +33088,7 @@
         <v>1396</v>
       </c>
       <c r="B1398" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1398" t="n">
         <v>0</v>
@@ -33111,7 +33111,7 @@
         <v>1397</v>
       </c>
       <c r="B1399" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1399" t="n">
         <v>0</v>
@@ -33134,7 +33134,7 @@
         <v>1398</v>
       </c>
       <c r="B1400" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1400" t="n">
         <v>0</v>
@@ -33157,7 +33157,7 @@
         <v>1399</v>
       </c>
       <c r="B1401" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1401" t="n">
         <v>0</v>
@@ -33180,7 +33180,7 @@
         <v>1400</v>
       </c>
       <c r="B1402" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1402" t="n">
         <v>0</v>
@@ -33203,7 +33203,7 @@
         <v>1401</v>
       </c>
       <c r="B1403" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1403" t="n">
         <v>0</v>
@@ -33226,7 +33226,7 @@
         <v>1402</v>
       </c>
       <c r="B1404" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1404" t="n">
         <v>0</v>
@@ -33249,7 +33249,7 @@
         <v>1403</v>
       </c>
       <c r="B1405" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1405" t="n">
         <v>0</v>
@@ -33272,7 +33272,7 @@
         <v>1404</v>
       </c>
       <c r="B1406" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1406" t="n">
         <v>0</v>
@@ -33295,7 +33295,7 @@
         <v>1405</v>
       </c>
       <c r="B1407" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1407" t="n">
         <v>0</v>
@@ -33318,7 +33318,7 @@
         <v>1406</v>
       </c>
       <c r="B1408" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1408" t="n">
         <v>0</v>
@@ -33341,7 +33341,7 @@
         <v>1407</v>
       </c>
       <c r="B1409" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1409" t="n">
         <v>0</v>
@@ -33364,7 +33364,7 @@
         <v>1408</v>
       </c>
       <c r="B1410" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1410" t="n">
         <v>0</v>
@@ -33387,7 +33387,7 @@
         <v>1409</v>
       </c>
       <c r="B1411" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1411" t="n">
         <v>0</v>
@@ -33410,7 +33410,7 @@
         <v>1410</v>
       </c>
       <c r="B1412" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1412" t="n">
         <v>0</v>
@@ -33433,7 +33433,7 @@
         <v>1411</v>
       </c>
       <c r="B1413" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1413" t="n">
         <v>0</v>
@@ -33456,7 +33456,7 @@
         <v>1412</v>
       </c>
       <c r="B1414" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1414" t="n">
         <v>0</v>
@@ -33479,7 +33479,7 @@
         <v>1413</v>
       </c>
       <c r="B1415" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1415" t="n">
         <v>0</v>
@@ -33502,7 +33502,7 @@
         <v>1414</v>
       </c>
       <c r="B1416" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1416" t="n">
         <v>0</v>
@@ -33525,7 +33525,7 @@
         <v>1415</v>
       </c>
       <c r="B1417" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1417" t="n">
         <v>0</v>
@@ -33548,7 +33548,7 @@
         <v>1416</v>
       </c>
       <c r="B1418" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1418" t="n">
         <v>0</v>
@@ -33571,7 +33571,7 @@
         <v>1417</v>
       </c>
       <c r="B1419" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1419" t="n">
         <v>0</v>
@@ -33594,7 +33594,7 @@
         <v>1418</v>
       </c>
       <c r="B1420" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1420" t="n">
         <v>0</v>
@@ -33617,7 +33617,7 @@
         <v>1419</v>
       </c>
       <c r="B1421" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1421" t="n">
         <v>0</v>
@@ -33640,7 +33640,7 @@
         <v>1420</v>
       </c>
       <c r="B1422" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1422" t="n">
         <v>0</v>
@@ -33663,7 +33663,7 @@
         <v>1421</v>
       </c>
       <c r="B1423" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1423" t="n">
         <v>0</v>
@@ -33686,7 +33686,7 @@
         <v>1422</v>
       </c>
       <c r="B1424" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1424" t="n">
         <v>0</v>
@@ -33709,7 +33709,7 @@
         <v>1423</v>
       </c>
       <c r="B1425" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1425" t="n">
         <v>0</v>
@@ -33732,7 +33732,7 @@
         <v>1424</v>
       </c>
       <c r="B1426" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1426" t="n">
         <v>0</v>
@@ -33755,7 +33755,7 @@
         <v>1425</v>
       </c>
       <c r="B1427" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1427" t="n">
         <v>0</v>
@@ -33778,7 +33778,7 @@
         <v>1426</v>
       </c>
       <c r="B1428" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1428" t="n">
         <v>0</v>
@@ -33801,7 +33801,7 @@
         <v>1427</v>
       </c>
       <c r="B1429" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1429" t="n">
         <v>0</v>
@@ -33824,7 +33824,7 @@
         <v>1428</v>
       </c>
       <c r="B1430" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1430" t="n">
         <v>0</v>
@@ -33847,7 +33847,7 @@
         <v>1429</v>
       </c>
       <c r="B1431" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1431" t="n">
         <v>0</v>
@@ -33870,7 +33870,7 @@
         <v>1430</v>
       </c>
       <c r="B1432" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1432" t="n">
         <v>0</v>
@@ -33893,7 +33893,7 @@
         <v>1431</v>
       </c>
       <c r="B1433" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1433" t="n">
         <v>0</v>
@@ -33916,7 +33916,7 @@
         <v>1432</v>
       </c>
       <c r="B1434" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1434" t="n">
         <v>0</v>
@@ -33939,7 +33939,7 @@
         <v>1433</v>
       </c>
       <c r="B1435" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1435" t="n">
         <v>0</v>
@@ -33962,7 +33962,7 @@
         <v>1434</v>
       </c>
       <c r="B1436" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1436" t="n">
         <v>0</v>
@@ -33985,7 +33985,7 @@
         <v>1435</v>
       </c>
       <c r="B1437" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1437" t="n">
         <v>0</v>
@@ -34008,7 +34008,7 @@
         <v>1436</v>
       </c>
       <c r="B1438" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1438" t="n">
         <v>0</v>
@@ -34031,7 +34031,7 @@
         <v>1437</v>
       </c>
       <c r="B1439" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1439" t="n">
         <v>0</v>
@@ -34054,7 +34054,7 @@
         <v>1438</v>
       </c>
       <c r="B1440" t="n">
-        <v>836.157331737603</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C1440" t="n">
         <v>0</v>
@@ -34131,7 +34131,7 @@
         <v>46132</v>
       </c>
       <c r="B2" t="n">
-        <v>57.22901059157841</v>
+        <v>104.4125548953759</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -34142,7 +34142,7 @@
         <v>46132.01041666666</v>
       </c>
       <c r="B3" t="n">
-        <v>8.752118644067796</v>
+        <v>555.521186440677</v>
       </c>
       <c r="C3" t="n">
         <v>15</v>
@@ -34153,7 +34153,7 @@
         <v>46132.02083333334</v>
       </c>
       <c r="B4" t="n">
-        <v>9.517441018960776</v>
+        <v>623.1131856998114</v>
       </c>
       <c r="C4" t="n">
         <v>30</v>
@@ -34164,7 +34164,7 @@
         <v>46132.03125</v>
       </c>
       <c r="B5" t="n">
-        <v>10.24683544303798</v>
+        <v>530.468354430379</v>
       </c>
       <c r="C5" t="n">
         <v>45</v>
@@ -34175,7 +34175,7 @@
         <v>46132.04166666666</v>
       </c>
       <c r="B6" t="n">
-        <v>8.755794462747817</v>
+        <v>775.4963007918615</v>
       </c>
       <c r="C6" t="n">
         <v>60</v>
@@ -34186,7 +34186,7 @@
         <v>46132.05208333334</v>
       </c>
       <c r="B7" t="n">
-        <v>9.504693016447085</v>
+        <v>622.9857056746745</v>
       </c>
       <c r="C7" t="n">
         <v>75</v>
@@ -34197,7 +34197,7 @@
         <v>46132.0625</v>
       </c>
       <c r="B8" t="n">
-        <v>8.813762479684234</v>
+        <v>565.5828302762934</v>
       </c>
       <c r="C8" t="n">
         <v>90</v>
@@ -34208,7 +34208,7 @@
         <v>46132.07291666666</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>676</v>
       </c>
       <c r="C9" t="n">
         <v>105</v>
@@ -34230,7 +34230,7 @@
         <v>46132.09375</v>
       </c>
       <c r="B11" t="n">
-        <v>8.006802721088436</v>
+        <v>553.0068027210884</v>
       </c>
       <c r="C11" t="n">
         <v>135</v>
@@ -34373,7 +34373,7 @@
         <v>46132.22916666666</v>
       </c>
       <c r="B24" t="n">
-        <v>10.40830053994692</v>
+        <v>398.042829687929</v>
       </c>
       <c r="C24" t="n">
         <v>330</v>
@@ -34384,7 +34384,7 @@
         <v>46132.23958333334</v>
       </c>
       <c r="B25" t="n">
-        <v>215.3128627815185</v>
+        <v>449.2588611094047</v>
       </c>
       <c r="C25" t="n">
         <v>345</v>
@@ -34395,7 +34395,7 @@
         <v>46132.25</v>
       </c>
       <c r="B26" t="n">
-        <v>101.5577463174185</v>
+        <v>496.4294752728117</v>
       </c>
       <c r="C26" t="n">
         <v>360</v>
@@ -34406,7 +34406,7 @@
         <v>46132.26041666666</v>
       </c>
       <c r="B27" t="n">
-        <v>336.0704038937751</v>
+        <v>718.7186278766821</v>
       </c>
       <c r="C27" t="n">
         <v>375</v>
@@ -34417,7 +34417,7 @@
         <v>46132.27083333334</v>
       </c>
       <c r="B28" t="n">
-        <v>212.0648259303722</v>
+        <v>630.1214156548688</v>
       </c>
       <c r="C28" t="n">
         <v>390</v>
@@ -34428,7 +34428,7 @@
         <v>46132.28125</v>
       </c>
       <c r="B29" t="n">
-        <v>109.2073739434567</v>
+        <v>875.9415062713135</v>
       </c>
       <c r="C29" t="n">
         <v>405</v>
@@ -34439,7 +34439,7 @@
         <v>46132.29166666666</v>
       </c>
       <c r="B30" t="n">
-        <v>107.8955333099169</v>
+        <v>722.115889254956</v>
       </c>
       <c r="C30" t="n">
         <v>420</v>
@@ -34450,7 +34450,7 @@
         <v>46132.30208333334</v>
       </c>
       <c r="B31" t="n">
-        <v>106.3884009299922</v>
+        <v>663.1606422229898</v>
       </c>
       <c r="C31" t="n">
         <v>435</v>
@@ -35033,7 +35033,7 @@
         <v>46132.85416666666</v>
       </c>
       <c r="B84" t="n">
-        <v>1087.644616961642</v>
+        <v>1486.545715862741</v>
       </c>
       <c r="C84" t="n">
         <v>1230</v>
@@ -35044,7 +35044,7 @@
         <v>46132.86458333334</v>
       </c>
       <c r="B85" t="n">
-        <v>3555.754366474405</v>
+        <v>3973.161773881813</v>
       </c>
       <c r="C85" t="n">
         <v>1245</v>
@@ -35055,7 +35055,7 @@
         <v>46132.875</v>
       </c>
       <c r="B86" t="n">
-        <v>2653.131698518605</v>
+        <v>3122.135388555506</v>
       </c>
       <c r="C86" t="n">
         <v>1260</v>
@@ -35066,7 +35066,7 @@
         <v>46132.88541666666</v>
       </c>
       <c r="B87" t="n">
-        <v>1447.151119915766</v>
+        <v>1834.890583517299</v>
       </c>
       <c r="C87" t="n">
         <v>1275</v>
@@ -35077,7 +35077,7 @@
         <v>46132.89583333334</v>
       </c>
       <c r="B88" t="n">
-        <v>1236.411716149647</v>
+        <v>1625.987005724937</v>
       </c>
       <c r="C88" t="n">
         <v>1290</v>
@@ -35088,7 +35088,7 @@
         <v>46132.90625</v>
       </c>
       <c r="B89" t="n">
-        <v>1936.821773691955</v>
+        <v>2332.945804699707</v>
       </c>
       <c r="C89" t="n">
         <v>1305</v>
@@ -35099,7 +35099,7 @@
         <v>46132.91666666666</v>
       </c>
       <c r="B90" t="n">
-        <v>2967.617641614217</v>
+        <v>3367.617641614217</v>
       </c>
       <c r="C90" t="n">
         <v>1320</v>
@@ -35110,7 +35110,7 @@
         <v>46132.92708333334</v>
       </c>
       <c r="B91" t="n">
-        <v>1181.732162691067</v>
+        <v>1583.662664621569</v>
       </c>
       <c r="C91" t="n">
         <v>1335</v>
@@ -35121,7 +35121,7 @@
         <v>46132.9375</v>
       </c>
       <c r="B92" t="n">
-        <v>984.0362564129688</v>
+        <v>1382.105754482467</v>
       </c>
       <c r="C92" t="n">
         <v>1350</v>
@@ -35132,7 +35132,7 @@
         <v>46132.94791666666</v>
       </c>
       <c r="B93" t="n">
-        <v>1666.838512483681</v>
+        <v>2066.063318685231</v>
       </c>
       <c r="C93" t="n">
         <v>1365</v>
@@ -35143,7 +35143,7 @@
         <v>46132.95833333334</v>
       </c>
       <c r="B94" t="n">
-        <v>1515.640754586284</v>
+        <v>1913.717677663207</v>
       </c>
       <c r="C94" t="n">
         <v>1380</v>
@@ -35154,7 +35154,7 @@
         <v>46132.96875</v>
       </c>
       <c r="B95" t="n">
-        <v>1650.943736628668</v>
+        <v>2048.25142893636</v>
       </c>
       <c r="C95" t="n">
         <v>1395</v>
@@ -35165,7 +35165,7 @@
         <v>46132.97916666666</v>
       </c>
       <c r="B96" t="n">
-        <v>1522.805298927472</v>
+        <v>1919.704523733673</v>
       </c>
       <c r="C96" t="n">
         <v>1410</v>
@@ -35176,7 +35176,7 @@
         <v>46132.98958333334</v>
       </c>
       <c r="B97" t="n">
-        <v>1030.575342465753</v>
+        <v>1430.575342465753</v>
       </c>
       <c r="C97" t="n">
         <v>1425</v>
@@ -35193,7 +35193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35233,62 +35233,62 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>575.487296200834</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>空调</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
         <v>-61.84251234740471</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>热水器</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>105</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1020.245726495726</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>空调</t>
-        </is>
-      </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120</v>
+        <v>330</v>
       </c>
       <c r="B4" t="n">
-        <v>-1020.245726495726</v>
+        <v>99.70783827229522</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>空调</t>
+          <t>热水器</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.2550614316239315</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -35296,10 +35296,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135</v>
+        <v>480</v>
       </c>
       <c r="B5" t="n">
-        <v>437.4174936111494</v>
+        <v>-575.487296200834</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -35310,7 +35310,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>4.603898369606672</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -35318,21 +35318,21 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>315</v>
+        <v>570</v>
       </c>
       <c r="B6" t="n">
-        <v>-437.4174936111494</v>
+        <v>-99.70783827229522</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>空调</t>
+          <t>热水器</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.312252480833448</v>
+        <v>0.3988313530891809</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -35340,17 +35340,17 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>329</v>
+        <v>810</v>
       </c>
       <c r="B7" t="n">
-        <v>135.3813559322035</v>
+        <v>99.60513931600036</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>空调</t>
+          <t>热水器</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -35362,10 +35362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>330</v>
+        <v>900</v>
       </c>
       <c r="B8" t="n">
-        <v>99.70783827229522</v>
+        <v>-99.60513931600036</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -35376,7 +35376,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.1494077089740005</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -35384,21 +35384,21 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>345</v>
+        <v>945</v>
       </c>
       <c r="B9" t="n">
-        <v>-135.3813559322035</v>
+        <v>104.6947853884265</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>空调</t>
+          <t>热水器</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03610169491525426</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -35406,17 +35406,17 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>360</v>
+        <v>1125</v>
       </c>
       <c r="B10" t="n">
-        <v>168.4349618508491</v>
+        <v>231.0002233472305</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>空调</t>
+          <t>电饭煲</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -35428,10 +35428,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>390</v>
+        <v>1214</v>
       </c>
       <c r="B11" t="n">
-        <v>-168.4349618508491</v>
+        <v>1254.235997606404</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -35442,7 +35442,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.08421748092542455</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -35450,375 +35450,199 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>435</v>
+        <v>1215</v>
       </c>
       <c r="B12" t="n">
-        <v>165.3763828763829</v>
+        <v>709.3207976705764</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
+        <is>
+          <t>洗碗机</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1230</v>
+      </c>
+      <c r="B13" t="n">
+        <v>441.543286801147</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>洗衣机</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1320</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-709.3207976705764</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>洗碗机</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1.241311395923509</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1335</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-441.543286801147</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>洗衣机</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7727007519020074</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1350</v>
+      </c>
+      <c r="B16" t="n">
+        <v>604.7071539764745</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>烘干机</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1365</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-231.0002233472305</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>电饭煲</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.924000893388922</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1395</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-104.6947853884265</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>热水器</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7852108904131987</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1425</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-604.7071539764745</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>烘干机</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7558839424705931</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1439</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-1254.235997606404</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>空调</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>480</v>
-      </c>
-      <c r="B13" t="n">
-        <v>-165.3763828763829</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>空调</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>0.1240322871572872</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>570</v>
-      </c>
-      <c r="B14" t="n">
-        <v>-99.70783827229522</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>热水器</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>0.3988313530891809</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>810</v>
-      </c>
-      <c r="B15" t="n">
-        <v>99.60513931600036</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>热水器</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>900</v>
-      </c>
-      <c r="B16" t="n">
-        <v>-99.60513931600036</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>热水器</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>0.1494077089740005</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>945</v>
-      </c>
-      <c r="B17" t="n">
-        <v>104.6947853884265</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>热水器</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>1125</v>
-      </c>
-      <c r="B18" t="n">
-        <v>231.0002233472305</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>电饭煲</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>1214</v>
-      </c>
-      <c r="B19" t="n">
-        <v>836.157331737603</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>空调</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>1215</v>
-      </c>
-      <c r="B20" t="n">
-        <v>709.3207976705764</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>洗碗机</t>
-        </is>
-      </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>4.703384991024016</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>1230</v>
-      </c>
-      <c r="B21" t="n">
-        <v>441.543286801147</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>洗衣机</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>1320</v>
-      </c>
-      <c r="B22" t="n">
-        <v>-709.3207976705764</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>洗碗机</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>1.241311395923509</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>1335</v>
-      </c>
-      <c r="B23" t="n">
-        <v>-441.543286801147</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>洗衣机</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0.7727007519020074</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1350</v>
-      </c>
-      <c r="B24" t="n">
-        <v>604.7071539764745</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>烘干机</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>1365</v>
-      </c>
-      <c r="B25" t="n">
-        <v>-231.0002233472305</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>电饭煲</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>0.924000893388922</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>1395</v>
-      </c>
-      <c r="B26" t="n">
-        <v>-104.6947853884265</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>热水器</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0.7852108904131987</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>1425</v>
-      </c>
-      <c r="B27" t="n">
-        <v>-604.7071539764745</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>烘干机</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>0.7558839424705931</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>1439</v>
-      </c>
-      <c r="B28" t="n">
-        <v>-836.157331737603</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>空调</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>3.135589994016011</v>
-      </c>
-      <c r="F28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -35833,7 +35657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA28"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35894,34 +35718,10 @@
       <c r="S1" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="n">
-        <v>26</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -35930,7 +35730,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -35975,30 +35775,6 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -36007,10 +35783,10 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -36058,30 +35834,6 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -36090,7 +35842,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -36099,7 +35851,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -36141,36 +35893,12 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
@@ -36182,7 +35910,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -36224,30 +35952,6 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -36259,10 +35963,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -36309,30 +36013,6 @@
       <c r="S6" t="n">
         <v>0</v>
       </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -36354,10 +36034,10 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -36390,30 +36070,6 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -36434,7 +36090,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -36455,7 +36111,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -36473,30 +36129,6 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -36517,7 +36149,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -36550,36 +36182,12 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -36612,26 +36220,26 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
@@ -36639,30 +36247,6 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -36692,7 +36276,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -36722,31 +36306,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -36784,11 +36344,11 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
@@ -36805,30 +36365,6 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -36864,7 +36400,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
@@ -36873,7 +36409,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -36888,30 +36424,6 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -36935,19 +36447,19 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -36973,30 +36485,6 @@
       <c r="S14" t="n">
         <v>0</v>
       </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -37033,7 +36521,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -37042,7 +36530,7 @@
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -37054,30 +36542,6 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -37122,7 +36586,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
@@ -37134,33 +36598,9 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -37190,7 +36630,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -37222,30 +36662,6 @@
       <c r="S17" t="n">
         <v>0</v>
       </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -37270,7 +36686,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -37305,30 +36721,6 @@
       <c r="S18" t="n">
         <v>0</v>
       </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -37374,7 +36766,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -37388,30 +36780,6 @@
       <c r="S19" t="n">
         <v>0</v>
       </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -37442,7 +36810,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -37469,694 +36837,6 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>0</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>0</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>0</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>0</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>0</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>0</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>0</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>0</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
         <v>1</v>
       </c>
     </row>
